--- a/output/stock_quant_scores/INTU_info.xlsx
+++ b/output/stock_quant_scores/INTU_info.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:FP2"/>
+  <dimension ref="A1:FT2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1051,235 +1051,255 @@
       </c>
       <c r="DV1" s="1" t="inlineStr">
         <is>
+          <t>shortName</t>
+        </is>
+      </c>
+      <c r="DW1" s="1" t="inlineStr">
+        <is>
+          <t>longName</t>
+        </is>
+      </c>
+      <c r="DX1" s="1" t="inlineStr">
+        <is>
+          <t>corporateActions</t>
+        </is>
+      </c>
+      <c r="DY1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketTime</t>
+        </is>
+      </c>
+      <c r="DZ1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketTime</t>
+        </is>
+      </c>
+      <c r="EA1" s="1" t="inlineStr">
+        <is>
+          <t>exchange</t>
+        </is>
+      </c>
+      <c r="EB1" s="1" t="inlineStr">
+        <is>
+          <t>messageBoardId</t>
+        </is>
+      </c>
+      <c r="EC1" s="1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneName</t>
+        </is>
+      </c>
+      <c r="ED1" s="1" t="inlineStr">
+        <is>
+          <t>exchangeTimezoneShortName</t>
+        </is>
+      </c>
+      <c r="EE1" s="1" t="inlineStr">
+        <is>
+          <t>gmtOffSetMilliseconds</t>
+        </is>
+      </c>
+      <c r="EF1" s="1" t="inlineStr">
+        <is>
+          <t>market</t>
+        </is>
+      </c>
+      <c r="EG1" s="1" t="inlineStr">
+        <is>
+          <t>esgPopulated</t>
+        </is>
+      </c>
+      <c r="EH1" s="1" t="inlineStr">
+        <is>
           <t>marketState</t>
         </is>
       </c>
-      <c r="DW1" s="1" t="inlineStr">
-        <is>
-          <t>corporateActions</t>
-        </is>
-      </c>
-      <c r="DX1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketTime</t>
-        </is>
-      </c>
-      <c r="DY1" s="1" t="inlineStr">
-        <is>
-          <t>exchange</t>
-        </is>
-      </c>
-      <c r="DZ1" s="1" t="inlineStr">
+      <c r="EI1" s="1" t="inlineStr">
         <is>
           <t>regularMarketChangePercent</t>
         </is>
       </c>
-      <c r="EA1" s="1" t="inlineStr">
+      <c r="EJ1" s="1" t="inlineStr">
         <is>
           <t>regularMarketPrice</t>
         </is>
       </c>
-      <c r="EB1" s="1" t="inlineStr">
+      <c r="EK1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketChangePercent</t>
+        </is>
+      </c>
+      <c r="EL1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketPrice</t>
+        </is>
+      </c>
+      <c r="EM1" s="1" t="inlineStr">
+        <is>
+          <t>postMarketChange</t>
+        </is>
+      </c>
+      <c r="EN1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketChange</t>
+        </is>
+      </c>
+      <c r="EO1" s="1" t="inlineStr">
+        <is>
+          <t>regularMarketDayRange</t>
+        </is>
+      </c>
+      <c r="EP1" s="1" t="inlineStr">
         <is>
           <t>fullExchangeName</t>
         </is>
       </c>
-      <c r="EC1" s="1" t="inlineStr">
+      <c r="EQ1" s="1" t="inlineStr">
         <is>
           <t>averageDailyVolume3Month</t>
         </is>
       </c>
-      <c r="ED1" s="1" t="inlineStr">
+      <c r="ER1" s="1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChange</t>
         </is>
       </c>
-      <c r="EE1" s="1" t="inlineStr">
+      <c r="ES1" s="1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekLowChangePercent</t>
         </is>
       </c>
-      <c r="EF1" s="1" t="inlineStr">
+      <c r="ET1" s="1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekRange</t>
         </is>
       </c>
-      <c r="EG1" s="1" t="inlineStr">
+      <c r="EU1" s="1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChange</t>
         </is>
       </c>
-      <c r="EH1" s="1" t="inlineStr">
+      <c r="EV1" s="1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekHighChangePercent</t>
         </is>
       </c>
-      <c r="EI1" s="1" t="inlineStr">
+      <c r="EW1" s="1" t="inlineStr">
         <is>
           <t>fiftyTwoWeekChangePercent</t>
         </is>
       </c>
-      <c r="EJ1" s="1" t="inlineStr">
+      <c r="EX1" s="1" t="inlineStr">
         <is>
           <t>dividendDate</t>
         </is>
       </c>
-      <c r="EK1" s="1" t="inlineStr">
-        <is>
-          <t>shortName</t>
-        </is>
-      </c>
-      <c r="EL1" s="1" t="inlineStr">
-        <is>
-          <t>longName</t>
-        </is>
-      </c>
-      <c r="EM1" s="1" t="inlineStr">
-        <is>
-          <t>messageBoardId</t>
-        </is>
-      </c>
-      <c r="EN1" s="1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneName</t>
-        </is>
-      </c>
-      <c r="EO1" s="1" t="inlineStr">
-        <is>
-          <t>exchangeTimezoneShortName</t>
-        </is>
-      </c>
-      <c r="EP1" s="1" t="inlineStr">
-        <is>
-          <t>gmtOffSetMilliseconds</t>
-        </is>
-      </c>
-      <c r="EQ1" s="1" t="inlineStr">
-        <is>
-          <t>market</t>
-        </is>
-      </c>
-      <c r="ER1" s="1" t="inlineStr">
-        <is>
-          <t>esgPopulated</t>
-        </is>
-      </c>
-      <c r="ES1" s="1" t="inlineStr">
+      <c r="EY1" s="1" t="inlineStr">
+        <is>
+          <t>earningsTimestamp</t>
+        </is>
+      </c>
+      <c r="EZ1" s="1" t="inlineStr">
+        <is>
+          <t>earningsTimestampStart</t>
+        </is>
+      </c>
+      <c r="FA1" s="1" t="inlineStr">
+        <is>
+          <t>earningsTimestampEnd</t>
+        </is>
+      </c>
+      <c r="FB1" s="1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampStart</t>
+        </is>
+      </c>
+      <c r="FC1" s="1" t="inlineStr">
+        <is>
+          <t>earningsCallTimestampEnd</t>
+        </is>
+      </c>
+      <c r="FD1" s="1" t="inlineStr">
+        <is>
+          <t>isEarningsDateEstimate</t>
+        </is>
+      </c>
+      <c r="FE1" s="1" t="inlineStr">
+        <is>
+          <t>epsTrailingTwelveMonths</t>
+        </is>
+      </c>
+      <c r="FF1" s="1" t="inlineStr">
+        <is>
+          <t>epsForward</t>
+        </is>
+      </c>
+      <c r="FG1" s="1" t="inlineStr">
+        <is>
+          <t>epsCurrentYear</t>
+        </is>
+      </c>
+      <c r="FH1" s="1" t="inlineStr">
+        <is>
+          <t>priceEpsCurrentYear</t>
+        </is>
+      </c>
+      <c r="FI1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChange</t>
+        </is>
+      </c>
+      <c r="FJ1" s="1" t="inlineStr">
+        <is>
+          <t>fiftyDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="FK1" s="1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChange</t>
+        </is>
+      </c>
+      <c r="FL1" s="1" t="inlineStr">
+        <is>
+          <t>twoHundredDayAverageChangePercent</t>
+        </is>
+      </c>
+      <c r="FM1" s="1" t="inlineStr">
+        <is>
+          <t>sourceInterval</t>
+        </is>
+      </c>
+      <c r="FN1" s="1" t="inlineStr">
+        <is>
+          <t>exchangeDataDelayedBy</t>
+        </is>
+      </c>
+      <c r="FO1" s="1" t="inlineStr">
+        <is>
+          <t>averageAnalystRating</t>
+        </is>
+      </c>
+      <c r="FP1" s="1" t="inlineStr">
+        <is>
+          <t>cryptoTradeable</t>
+        </is>
+      </c>
+      <c r="FQ1" s="1" t="inlineStr">
         <is>
           <t>hasPrePostMarketData</t>
         </is>
       </c>
-      <c r="ET1" s="1" t="inlineStr">
+      <c r="FR1" s="1" t="inlineStr">
         <is>
           <t>firstTradeDateMilliseconds</t>
         </is>
       </c>
-      <c r="EU1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketChange</t>
-        </is>
-      </c>
-      <c r="EV1" s="1" t="inlineStr">
-        <is>
-          <t>regularMarketDayRange</t>
-        </is>
-      </c>
-      <c r="EW1" s="1" t="inlineStr">
-        <is>
-          <t>earningsTimestamp</t>
-        </is>
-      </c>
-      <c r="EX1" s="1" t="inlineStr">
-        <is>
-          <t>earningsTimestampStart</t>
-        </is>
-      </c>
-      <c r="EY1" s="1" t="inlineStr">
-        <is>
-          <t>earningsTimestampEnd</t>
-        </is>
-      </c>
-      <c r="EZ1" s="1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampStart</t>
-        </is>
-      </c>
-      <c r="FA1" s="1" t="inlineStr">
-        <is>
-          <t>earningsCallTimestampEnd</t>
-        </is>
-      </c>
-      <c r="FB1" s="1" t="inlineStr">
-        <is>
-          <t>isEarningsDateEstimate</t>
-        </is>
-      </c>
-      <c r="FC1" s="1" t="inlineStr">
-        <is>
-          <t>epsTrailingTwelveMonths</t>
-        </is>
-      </c>
-      <c r="FD1" s="1" t="inlineStr">
-        <is>
-          <t>epsForward</t>
-        </is>
-      </c>
-      <c r="FE1" s="1" t="inlineStr">
-        <is>
-          <t>epsCurrentYear</t>
-        </is>
-      </c>
-      <c r="FF1" s="1" t="inlineStr">
-        <is>
-          <t>priceEpsCurrentYear</t>
-        </is>
-      </c>
-      <c r="FG1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChange</t>
-        </is>
-      </c>
-      <c r="FH1" s="1" t="inlineStr">
-        <is>
-          <t>fiftyDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="FI1" s="1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChange</t>
-        </is>
-      </c>
-      <c r="FJ1" s="1" t="inlineStr">
-        <is>
-          <t>twoHundredDayAverageChangePercent</t>
-        </is>
-      </c>
-      <c r="FK1" s="1" t="inlineStr">
-        <is>
-          <t>sourceInterval</t>
-        </is>
-      </c>
-      <c r="FL1" s="1" t="inlineStr">
-        <is>
-          <t>exchangeDataDelayedBy</t>
-        </is>
-      </c>
-      <c r="FM1" s="1" t="inlineStr">
-        <is>
-          <t>averageAnalystRating</t>
-        </is>
-      </c>
-      <c r="FN1" s="1" t="inlineStr">
-        <is>
-          <t>cryptoTradeable</t>
-        </is>
-      </c>
-      <c r="FO1" s="1" t="inlineStr">
+      <c r="FS1" s="1" t="inlineStr">
         <is>
           <t>displayName</t>
         </is>
       </c>
-      <c r="FP1" s="1" t="inlineStr">
+      <c r="FT1" s="1" t="inlineStr">
         <is>
           <t>trailingPegRatio</t>
         </is>
@@ -1405,28 +1425,28 @@
         <v>2</v>
       </c>
       <c r="AC2" t="n">
-        <v>699.1799999999999</v>
+        <v>692.6799999999999</v>
       </c>
       <c r="AD2" t="n">
-        <v>703.71</v>
+        <v>692.6900000000001</v>
       </c>
       <c r="AE2" t="n">
-        <v>688.96</v>
+        <v>690.41</v>
       </c>
       <c r="AF2" t="n">
-        <v>703.71</v>
+        <v>700</v>
       </c>
       <c r="AG2" t="n">
-        <v>699.1799999999999</v>
+        <v>692.6799999999999</v>
       </c>
       <c r="AH2" t="n">
-        <v>703.71</v>
+        <v>692.6900000000001</v>
       </c>
       <c r="AI2" t="n">
-        <v>688.96</v>
+        <v>690.41</v>
       </c>
       <c r="AJ2" t="n">
-        <v>703.71</v>
+        <v>700</v>
       </c>
       <c r="AK2" t="n">
         <v>4.32</v>
@@ -1447,31 +1467,31 @@
         <v>1.26</v>
       </c>
       <c r="AQ2" t="n">
-        <v>50.53577</v>
+        <v>51.005116</v>
       </c>
       <c r="AR2" t="n">
-        <v>31.144402</v>
+        <v>31.410707</v>
       </c>
       <c r="AS2" t="n">
-        <v>1049582</v>
+        <v>1474667</v>
       </c>
       <c r="AT2" t="n">
-        <v>1049582</v>
+        <v>1474667</v>
       </c>
       <c r="AU2" t="n">
-        <v>1879936</v>
+        <v>1876020</v>
       </c>
       <c r="AV2" t="n">
-        <v>2485600</v>
+        <v>2241950</v>
       </c>
       <c r="AW2" t="n">
-        <v>2485600</v>
+        <v>2241950</v>
       </c>
       <c r="AX2" t="n">
-        <v>658.5599999999999</v>
+        <v>697.61</v>
       </c>
       <c r="AY2" t="n">
-        <v>726.36</v>
+        <v>699.6799999999999</v>
       </c>
       <c r="AZ2" t="n">
         <v>1</v>
@@ -1480,7 +1500,7 @@
         <v>1</v>
       </c>
       <c r="BB2" t="n">
-        <v>193027850240</v>
+        <v>194678374400</v>
       </c>
       <c r="BC2" t="n">
         <v>532.65</v>
@@ -1495,19 +1515,19 @@
         <v>2</v>
       </c>
       <c r="BG2" t="n">
-        <v>10.250537</v>
+        <v>10.338186</v>
       </c>
       <c r="BH2" t="n">
-        <v>715.0844</v>
+        <v>711.7582</v>
       </c>
       <c r="BI2" t="n">
-        <v>665.04736</v>
+        <v>665.7269</v>
       </c>
       <c r="BJ2" t="n">
         <v>4.16</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.005949827</v>
+        <v>0.0060056592</v>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
@@ -1527,40 +1547,40 @@
         <v>278805000</v>
       </c>
       <c r="BQ2" t="n">
-        <v>4761374</v>
+        <v>4657282</v>
       </c>
       <c r="BR2" t="n">
-        <v>4684100</v>
+        <v>4707290</v>
       </c>
       <c r="BS2" t="n">
-        <v>1753920000</v>
+        <v>1755216000</v>
       </c>
       <c r="BT2" t="n">
-        <v>1756425600</v>
+        <v>1757894400</v>
       </c>
       <c r="BU2" t="n">
-        <v>0.0171</v>
+        <v>0.0167</v>
       </c>
       <c r="BV2" t="n">
         <v>0.02568</v>
       </c>
       <c r="BW2" t="n">
-        <v>0.89679</v>
+        <v>0.89705</v>
       </c>
       <c r="BX2" t="n">
-        <v>2.28</v>
+        <v>2.06</v>
       </c>
       <c r="BY2" t="n">
-        <v>0.0175</v>
+        <v>0.0171</v>
       </c>
       <c r="BZ2" t="n">
-        <v>279110016</v>
+        <v>279654279</v>
       </c>
       <c r="CA2" t="n">
         <v>70.613</v>
       </c>
       <c r="CB2" t="n">
-        <v>9.80471</v>
+        <v>9.888548</v>
       </c>
       <c r="CC2" t="n">
         <v>1753920000</v>
@@ -1578,7 +1598,7 @@
         <v>3868999936</v>
       </c>
       <c r="CH2" t="n">
-        <v>13.7</v>
+        <v>13.69</v>
       </c>
       <c r="CI2" t="n">
         <v>22.23</v>
@@ -1592,10 +1612,10 @@
         <v>1152230400</v>
       </c>
       <c r="CL2" t="n">
-        <v>0.10152185</v>
+        <v>0.12441218</v>
       </c>
       <c r="CM2" t="n">
-        <v>0.16333759</v>
+        <v>0.1529237</v>
       </c>
       <c r="CN2" t="n">
         <v>1.04</v>
@@ -1609,7 +1629,7 @@
         </is>
       </c>
       <c r="CQ2" t="n">
-        <v>692.34</v>
+        <v>698.26</v>
       </c>
       <c r="CR2" t="n">
         <v>971</v>
@@ -1719,172 +1739,184 @@
       </c>
       <c r="DV2" t="inlineStr">
         <is>
-          <t>REGULAR</t>
+          <t>Intuit Inc.</t>
         </is>
       </c>
       <c r="DW2" t="inlineStr">
         <is>
+          <t>Intuit Inc.</t>
+        </is>
+      </c>
+      <c r="DX2" t="inlineStr">
+        <is>
           <t>[{'header': 'Dividend', 'message': 'INTU announced a cash dividend of 1.20 with an ex-date of Oct. 9, 2025', 'meta': {'eventType': 'DIVIDEND', 'dateEpochMs': 1759982400000, 'amount': '1.20'}}]</t>
         </is>
       </c>
-      <c r="DX2" t="n">
-        <v>1758739996</v>
-      </c>
-      <c r="DY2" t="inlineStr">
+      <c r="DY2" t="n">
+        <v>1758930948</v>
+      </c>
+      <c r="DZ2" t="n">
+        <v>1758916801</v>
+      </c>
+      <c r="EA2" t="inlineStr">
         <is>
           <t>NMS</t>
         </is>
       </c>
-      <c r="DZ2" t="n">
-        <v>-0.978284</v>
-      </c>
-      <c r="EA2" t="n">
-        <v>692.34</v>
-      </c>
       <c r="EB2" t="inlineStr">
         <is>
+          <t>finmb_21171</t>
+        </is>
+      </c>
+      <c r="EC2" t="inlineStr">
+        <is>
+          <t>America/New_York</t>
+        </is>
+      </c>
+      <c r="ED2" t="inlineStr">
+        <is>
+          <t>EDT</t>
+        </is>
+      </c>
+      <c r="EE2" t="n">
+        <v>-14400000</v>
+      </c>
+      <c r="EF2" t="inlineStr">
+        <is>
+          <t>us_market</t>
+        </is>
+      </c>
+      <c r="EG2" t="b">
+        <v>0</v>
+      </c>
+      <c r="EH2" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="EI2" t="n">
+        <v>0.805569</v>
+      </c>
+      <c r="EJ2" t="n">
+        <v>698.26</v>
+      </c>
+      <c r="EK2" t="n">
+        <v>-0.03436975</v>
+      </c>
+      <c r="EL2" t="n">
+        <v>698.02</v>
+      </c>
+      <c r="EM2" t="n">
+        <v>-0.23999023</v>
+      </c>
+      <c r="EN2" t="n">
+        <v>5.58002</v>
+      </c>
+      <c r="EO2" t="inlineStr">
+        <is>
+          <t>690.41 - 700.0</t>
+        </is>
+      </c>
+      <c r="EP2" t="inlineStr">
+        <is>
           <t>NasdaqGS</t>
         </is>
       </c>
-      <c r="EC2" t="n">
-        <v>1879936</v>
-      </c>
-      <c r="ED2" t="n">
-        <v>159.69</v>
-      </c>
-      <c r="EE2" t="n">
-        <v>0.29980287</v>
-      </c>
-      <c r="EF2" t="inlineStr">
+      <c r="EQ2" t="n">
+        <v>1876020</v>
+      </c>
+      <c r="ER2" t="n">
+        <v>165.60999</v>
+      </c>
+      <c r="ES2" t="n">
+        <v>0.31091708</v>
+      </c>
+      <c r="ET2" t="inlineStr">
         <is>
           <t>532.65 - 813.7</t>
         </is>
       </c>
-      <c r="EG2" t="n">
-        <v>-121.359985</v>
-      </c>
-      <c r="EH2" t="n">
-        <v>-0.14914586</v>
-      </c>
-      <c r="EI2" t="n">
-        <v>10.152185</v>
-      </c>
-      <c r="EJ2" t="n">
+      <c r="EU2" t="n">
+        <v>-115.44</v>
+      </c>
+      <c r="EV2" t="n">
+        <v>-0.14187047</v>
+      </c>
+      <c r="EW2" t="n">
+        <v>12.441217</v>
+      </c>
+      <c r="EX2" t="n">
         <v>1760659200</v>
       </c>
-      <c r="EK2" t="inlineStr">
-        <is>
-          <t>Intuit Inc.</t>
-        </is>
-      </c>
-      <c r="EL2" t="inlineStr">
-        <is>
-          <t>Intuit Inc.</t>
-        </is>
-      </c>
-      <c r="EM2" t="inlineStr">
-        <is>
-          <t>finmb_21171</t>
-        </is>
-      </c>
-      <c r="EN2" t="inlineStr">
-        <is>
-          <t>America/New_York</t>
-        </is>
-      </c>
-      <c r="EO2" t="inlineStr">
-        <is>
-          <t>EDT</t>
-        </is>
-      </c>
-      <c r="EP2" t="n">
-        <v>-14400000</v>
-      </c>
-      <c r="EQ2" t="inlineStr">
-        <is>
-          <t>us_market</t>
-        </is>
-      </c>
-      <c r="ER2" t="b">
+      <c r="EY2" t="n">
+        <v>1755806400</v>
+      </c>
+      <c r="EZ2" t="n">
+        <v>1763668800</v>
+      </c>
+      <c r="FA2" t="n">
+        <v>1763668800</v>
+      </c>
+      <c r="FB2" t="n">
+        <v>1755808200</v>
+      </c>
+      <c r="FC2" t="n">
+        <v>1755808200</v>
+      </c>
+      <c r="FD2" t="b">
+        <v>1</v>
+      </c>
+      <c r="FE2" t="n">
+        <v>13.69</v>
+      </c>
+      <c r="FF2" t="n">
+        <v>22.23</v>
+      </c>
+      <c r="FG2" t="n">
+        <v>23.1542</v>
+      </c>
+      <c r="FH2" t="n">
+        <v>30.156948</v>
+      </c>
+      <c r="FI2" t="n">
+        <v>-13.498169</v>
+      </c>
+      <c r="FJ2" t="n">
+        <v>-0.018964544</v>
+      </c>
+      <c r="FK2" t="n">
+        <v>32.53308</v>
+      </c>
+      <c r="FL2" t="n">
+        <v>0.048868507</v>
+      </c>
+      <c r="FM2" t="n">
+        <v>15</v>
+      </c>
+      <c r="FN2" t="n">
         <v>0</v>
       </c>
-      <c r="ES2" t="b">
+      <c r="FO2" t="inlineStr">
+        <is>
+          <t>1.7 - Buy</t>
+        </is>
+      </c>
+      <c r="FP2" t="b">
+        <v>0</v>
+      </c>
+      <c r="FQ2" t="b">
         <v>1</v>
       </c>
-      <c r="ET2" t="n">
+      <c r="FR2" t="n">
         <v>731946600000</v>
       </c>
-      <c r="EU2" t="n">
-        <v>-6.839966</v>
-      </c>
-      <c r="EV2" t="inlineStr">
-        <is>
-          <t>688.96 - 703.71</t>
-        </is>
-      </c>
-      <c r="EW2" t="n">
-        <v>1755806400</v>
-      </c>
-      <c r="EX2" t="n">
-        <v>1763668800</v>
-      </c>
-      <c r="EY2" t="n">
-        <v>1763668800</v>
-      </c>
-      <c r="EZ2" t="n">
-        <v>1755808200</v>
-      </c>
-      <c r="FA2" t="n">
-        <v>1755808200</v>
-      </c>
-      <c r="FB2" t="b">
-        <v>1</v>
-      </c>
-      <c r="FC2" t="n">
-        <v>13.7</v>
-      </c>
-      <c r="FD2" t="n">
-        <v>22.23</v>
-      </c>
-      <c r="FE2" t="n">
-        <v>23.15434</v>
-      </c>
-      <c r="FF2" t="n">
-        <v>29.90109</v>
-      </c>
-      <c r="FG2" t="n">
-        <v>-22.744385</v>
-      </c>
-      <c r="FH2" t="n">
-        <v>-0.031806573</v>
-      </c>
-      <c r="FI2" t="n">
-        <v>27.292664</v>
-      </c>
-      <c r="FJ2" t="n">
-        <v>0.041038677</v>
-      </c>
-      <c r="FK2" t="n">
-        <v>15</v>
-      </c>
-      <c r="FL2" t="n">
-        <v>0</v>
-      </c>
-      <c r="FM2" t="inlineStr">
-        <is>
-          <t>1.7 - Buy</t>
-        </is>
-      </c>
-      <c r="FN2" t="b">
-        <v>0</v>
-      </c>
-      <c r="FO2" t="inlineStr">
+      <c r="FS2" t="inlineStr">
         <is>
           <t>Intuit</t>
         </is>
       </c>
-      <c r="FP2" t="n">
-        <v>1.9658</v>
+      <c r="FT2" t="n">
+        <v>1.9633</v>
       </c>
     </row>
   </sheetData>
